--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R609126b3525d4d66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="Rae6d4362738e4af4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R5366f940335d4852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6541125721148cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R6a945dd6da954051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="Rb8a2e4da5bc44c74"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46188.661470914354</x:v>
+        <x:v>46189.39364253472</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3139,7 +3139,7 @@
         <x:v>docs/en/part5/ch16_distillation.md</x:v>
       </x:c>
       <x:c r="G36" s="4" t="n">
-        <x:v>346</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
         <x:v>16-1</x:v>
@@ -3201,7 +3201,7 @@
         <x:v>docs/en/part5/ch16_distillation.md</x:v>
       </x:c>
       <x:c r="G37" s="4" t="n">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
         <x:v>16-2</x:v>
@@ -13105,16 +13105,16 @@
         <x:v>Figure P03-1</x:v>
       </x:c>
       <x:c r="K195" s="4" t="str">
-        <x:v>docs/images/part14/p03_01_llava_factory_overview.png</x:v>
+        <x:v>docs/images/part14/p03/p03_01_llava_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L195" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M195" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N195" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O195" s="4" t="str">
         <x:v>LLaVA Multimodal Instruction Data Factory Overview.</x:v>
@@ -13167,16 +13167,16 @@
         <x:v>Figure P03-2</x:v>
       </x:c>
       <x:c r="K196" s="4" t="str">
-        <x:v>docs/images/part14/p03_02_roles_and_responsibilities.png</x:v>
+        <x:v>docs/images/part14/p03/p03_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L196" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M196" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1344x768</x:v>
       </x:c>
       <x:c r="N196" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O196" s="4" t="str">
         <x:v>Multimodal Data Factory Responsibility Collaboration Diagram.</x:v>
@@ -13229,16 +13229,16 @@
         <x:v>Figure P03-3</x:v>
       </x:c>
       <x:c r="K197" s="4" t="str">
-        <x:v>docs/images/part14/p03_03_asset_layers.png</x:v>
+        <x:v>docs/images/part14/p03/p03_03_asset_layers.svg</x:v>
       </x:c>
       <x:c r="L197" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M197" s="4" t="str">
-        <x:v>2816x1332</x:v>
+        <x:v>1024x512</x:v>
       </x:c>
       <x:c r="N197" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O197" s="4" t="str">
         <x:v>Multimodal Asset Layering Diagram.</x:v>
@@ -13291,16 +13291,16 @@
         <x:v>Figure P03-4</x:v>
       </x:c>
       <x:c r="K198" s="4" t="str">
-        <x:v>docs/images/part14/p03_04_document_tasks.png</x:v>
+        <x:v>docs/images/part14/p03/p03_04_document_tasks.svg</x:v>
       </x:c>
       <x:c r="L198" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M198" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N198" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O198" s="4" t="str">
         <x:v>Document Image Task Layering Diagram.</x:v>
@@ -13353,16 +13353,16 @@
         <x:v>Figure P03-5</x:v>
       </x:c>
       <x:c r="K199" s="4" t="str">
-        <x:v>docs/images/part14/p03_05_bbox_alignment.png</x:v>
+        <x:v>docs/images/part14/p03/p03_05_bbox_alignment.svg</x:v>
       </x:c>
       <x:c r="L199" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M199" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1024x576</x:v>
       </x:c>
       <x:c r="N199" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O199" s="4" t="str">
         <x:v>Bounding Box Coordinate Conversion and Normalization Diagram.</x:v>
@@ -13415,16 +13415,16 @@
         <x:v>Figure P03-6</x:v>
       </x:c>
       <x:c r="K200" s="4" t="str">
-        <x:v>docs/images/part14/p03_06_quality_loop.png</x:v>
+        <x:v>docs/images/part14/p03/p03_06_quality_loop.svg</x:v>
       </x:c>
       <x:c r="L200" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M200" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N200" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O200" s="4" t="str">
         <x:v>Sample Quality Inspection and Rollback Closure Loop Diagram.</x:v>
@@ -13477,16 +13477,16 @@
         <x:v>Figure P03-7</x:v>
       </x:c>
       <x:c r="K201" s="4" t="str">
-        <x:v>docs/images/part14/p03_07_failure_attribution.png</x:v>
+        <x:v>docs/images/part14/p03/p03_07_failure_attribution.svg</x:v>
       </x:c>
       <x:c r="L201" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M201" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N201" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O201" s="4" t="str">
         <x:v>Failure Sample Attribution Diagram.</x:v>
@@ -13539,16 +13539,16 @@
         <x:v>Figure P03-8</x:v>
       </x:c>
       <x:c r="K202" s="4" t="str">
-        <x:v>docs/images/part14/p03_08_validation_loop.png</x:v>
+        <x:v>docs/images/part14/p03/p03_08_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L202" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M202" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N202" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O202" s="4" t="str">
         <x:v>Project Validation Closure Loop Diagram.</x:v>
@@ -18639,7 +18639,7 @@
         <x:v>docs/en/part14/p14_video_generation.md</x:v>
       </x:c>
       <x:c r="G284" s="4" t="n">
-        <x:v>518</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H284" s="4" t="str">
         <x:v>P14-2</x:v>
@@ -18701,7 +18701,7 @@
         <x:v>docs/en/part14/p14_video_generation.md</x:v>
       </x:c>
       <x:c r="G285" s="4" t="n">
-        <x:v>518</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H285" s="4" t="str">
         <x:v>P14-3</x:v>
